--- a/www/download/IND.value.m.mv.rpA1.xlsx
+++ b/www/download/IND.value.m.mv.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1084486.74287555</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1017496.16265025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1013213.67928478</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1136645.49451911</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1167921.42581459</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1192583.84156113</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1237006.79574061</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1173473.80758761</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>958285.370646604</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>884305.004716022</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>808730.122358965</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>775401.409514549</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>681643.25656848</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>641823.225846563</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>669798.308226838</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>999221.595945927</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1065109.58793996</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>1088801.94371989</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.107</t>
+          <t>1107330.96623396</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1147895.9664048</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>1305615.43839968</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1296908.95041578</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1180138.81366004</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>997869.316210358</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>894725.194713273</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>846881.986607965</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>830027.216702199</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>721874.927642947</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>569873.450284385</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>562272.859970893</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>857487.296019394</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>851035.82947548</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>897089.822720305</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>897510.708953096</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>946473.413755954</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>1038800.37506399</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1026701.9235561</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>969148.316886925</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>872736.759850047</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>806016.162739369</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>771634.74543987</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>739485.107784928</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>659716.973843257</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>678576.007466879</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>617677.736830407</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.228</t>
+          <t>9227583.77934562</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.764</t>
+          <t>8764466.85632641</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.205</t>
+          <t>10204993.7377435</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9149706.60045088</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.239</t>
+          <t>8238844.91239</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.843</t>
+          <t>7842736.19231323</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.002</t>
+          <t>7001740.68452406</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.114</t>
+          <t>6113709.43970825</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.631</t>
+          <t>4631436.79982781</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.939</t>
+          <t>3938567.48502766</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3660075.42927655</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.308</t>
+          <t>3307544.72722654</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.665</t>
+          <t>2664565.13899283</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.289</t>
+          <t>2289279.53893442</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>2435039.24788096</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.082</t>
+          <t>4082217.15015806</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.814</t>
+          <t>3814377.70759995</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.699</t>
+          <t>3698775.73970616</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.779</t>
+          <t>3778714.62488326</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.422</t>
+          <t>5421747.58117465</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.847</t>
+          <t>4847302.81272183</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.457</t>
+          <t>5457241.96169904</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.908</t>
+          <t>5908363.75706513</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5.441</t>
+          <t>5440785.41441968</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.777</t>
+          <t>4777222.02290553</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.926</t>
+          <t>3926056.03511829</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.306</t>
+          <t>3306216.4835335</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.703</t>
+          <t>2703252.79490355</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>2273852.72229662</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.382</t>
+          <t>2382092.57811332</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1176849.61781369</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1132630.39495403</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1090710.38998132</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>1152508.52047278</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.128</t>
+          <t>1128113.16337444</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1090405.70241931</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1169578.04991516</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1073374.58488591</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>971148.05942799</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>936252.827601979</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>901705.501108097</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>831743.873017825</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>732470.572352961</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>695126.253975801</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>711522.19321066</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24570469.9343153</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21619506.8947354</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.591</t>
+          <t>19591161.446176</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18.578</t>
+          <t>18578188.9559919</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>17109918.6338688</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.186</t>
+          <t>15186184.6047169</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13.977</t>
+          <t>13977055.4425753</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12.958</t>
+          <t>12958092.139646</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12210145.1420294</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11119727.9991544</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.921</t>
+          <t>9921141.64947175</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8.612</t>
+          <t>8611635.05760815</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6.968</t>
+          <t>6968275.81180289</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5.607</t>
+          <t>5606968.40774697</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5.332</t>
+          <t>5331596.21764542</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>2014922.49506886</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.074</t>
+          <t>2073634.45227557</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.028</t>
+          <t>2027754.96293714</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>2003163.69216738</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t>2253861.02407676</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2280379.06984167</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>2333848.38743778</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.137</t>
+          <t>2137141.61594983</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>1855583.72603838</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1619567.0940603</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1325558.83462851</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.241</t>
+          <t>1241322.95977889</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>1021395.6150515</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1192660.4433624</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>829152.958506358</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.471</t>
+          <t>3471064.41066479</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3229664.3023541</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.522</t>
+          <t>3522189.04216229</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>3221834.73538717</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.259</t>
+          <t>3258637.78690343</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.225</t>
+          <t>3224873.14968653</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>3001372.41834504</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.592</t>
+          <t>2591557.99557861</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2103332.20367204</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>1762450.75045421</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>1621512.68752259</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1478948.47535645</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1235364.68318941</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>971409.591976553</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>1036591.01354542</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>840588.715784752</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>814851.141992354</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>875271.408783115</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>896794.472758284</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>937364.632037623</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1077822.66875372</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.038</t>
+          <t>1037627.17957452</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>978716.768855591</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.868</t>
+          <t>868294.625616083</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>813188.741211826</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>788290.806613859</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>768123.065704967</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>690657.621643542</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>542855.251147825</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>553581.598585954</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>936228.079007942</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>917358.534686483</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1056771.30997451</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>969270.018032219</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>923421.027328864</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>970961.343004224</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1008713.76224346</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>916905.240398699</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>815192.113803176</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.748</t>
+          <t>747947.349101914</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>697982.353021427</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>639923.285944458</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564135.095427565</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>476698.220599423</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>481058.19058989</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1078883.94455116</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1056490.83017854</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.121</t>
+          <t>1121138.62831069</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1150019.46405198</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.249</t>
+          <t>1249077.42295963</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1399239.18465063</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1344446.64222705</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1239456.01171434</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1014213.74512879</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>911755.51388384</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>863011.61541281</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>822698.87994171</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>728123.146817365</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>601788.079114841</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>556671.614728427</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.343</t>
+          <t>6342577.74520556</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.241</t>
+          <t>5240600.13198879</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.365</t>
+          <t>5364593.93269759</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4.489</t>
+          <t>4488750.47294764</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.075</t>
+          <t>4074616.49564268</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>4192371.22513704</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.098</t>
+          <t>4098089.03432475</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.638</t>
+          <t>3638312.48486456</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>2967423.75106552</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>2646321.35752027</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>2183130.3759428</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.893</t>
+          <t>1893209.28975938</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1454064.3730377</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1285247.49856307</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1373423.28072482</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>987894.540243692</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>984791.736986844</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>998592.001260864</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1032262.54679044</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>1131833.22341389</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1173597.08680779</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1117487.877754</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1045164.32011892</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>932100.048139635</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>815831.668302057</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>796217.213247507</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>753937.533054768</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>636141.016245439</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>532710.525846113</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>491430.989517422</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>831525.530690498</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>827360.995382429</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>834851.351153632</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>839762.285674575</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>870064.625238459</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>955674.966193611</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>949930.910348725</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>885406.934609939</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>762666.176264715</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>693962.669523656</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>670942.775158312</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634436.723714253</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>562035.804314024</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>462949.632282726</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>440992.781562892</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>1037383.21174737</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1013295.92799507</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>912202.645540566</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>879089.166609563</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>884467.264429256</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>902133.421875561</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>914202.273110101</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>837917.023507115</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>754450.854696957</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>667848.683055849</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630944.216736841</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>593080.707818798</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>521749.836580374</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>477382.581002203</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529531.733217848</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.829</t>
+          <t>1829008.33129351</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.814</t>
+          <t>1813620.87473688</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>1871297.38500624</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1929869.39749789</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>1897487.99846669</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>2220630.9217287</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2029882.67614171</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.824</t>
+          <t>1824056.04638492</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1450639.27317391</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>1260541.12847616</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1166783.32387968</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1159325.03235088</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1024073.50961539</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>893977.934871889</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>942871.65173663</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.992</t>
+          <t>3992459.72772564</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>3836479.91861328</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>3717445.14857679</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.732</t>
+          <t>3731852.33005029</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.944</t>
+          <t>3944394.07200769</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.997</t>
+          <t>3997184.4902813</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.432</t>
+          <t>3432312.40718526</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.972</t>
+          <t>2972054.11670064</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.425</t>
+          <t>2425088.30303397</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>1882149.01318206</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>1747624.41114452</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.657</t>
+          <t>1656770.02351001</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1415344.37469779</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1044743.31130913</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1238603.87935504</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11.139</t>
+          <t>11138914.7533463</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.042</t>
+          <t>10041842.1259682</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.708</t>
+          <t>9708413.49373121</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>24.027</t>
+          <t>24026996.3297513</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16.295</t>
+          <t>16295421.5155601</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14.388</t>
+          <t>14388030.9473635</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14.907</t>
+          <t>14907252.2937106</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13.197</t>
+          <t>13197368.5525513</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11.281</t>
+          <t>11280770.6926913</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11.189</t>
+          <t>11189442.7592244</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9.403</t>
+          <t>9403016.04632278</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6.676</t>
+          <t>6675734.06412355</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>5.667</t>
+          <t>5666980.47176559</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4930099.01950721</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.892</t>
+          <t>4891803.19493737</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>30.349</t>
+          <t>30349231.8858274</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>29760371.6308332</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27.768</t>
+          <t>27768203.4903507</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>27.477</t>
+          <t>27477362.7145973</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>26.564</t>
+          <t>26563580.9590978</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27380245.6906075</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28.949</t>
+          <t>28949416.0035571</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>28.179</t>
+          <t>28178715.0604156</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>25.978</t>
+          <t>25977514.9721391</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>23.295</t>
+          <t>23295268.2247074</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>20.321</t>
+          <t>20321065.7874841</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>17789818.7632606</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>13.861</t>
+          <t>13861219.2663945</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>13.179</t>
+          <t>13178729.4434189</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>13.389</t>
+          <t>13389227.068146</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1177062.87625538</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1116771.01648273</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>1041016.50674497</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1011748.58539389</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.033</t>
+          <t>1032746.02664585</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1083916.15745634</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.047</t>
+          <t>1047314.05410566</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>929759.408222044</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>770470.914230476</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>713407.110587407</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>683002.652647757</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>621616.05752854</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>580668.528361092</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>525034.757522908</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>578120.105043187</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1105459.01499081</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.023</t>
+          <t>1022982.89392367</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1018082.89050096</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1032420.04725117</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1086250.92671948</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.199</t>
+          <t>1199252.82312264</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1190440.45624415</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1113694.89142682</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>956149.040810999</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870664.9914592</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>825934.262201341</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>829243.31155478</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>722284.470407279</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>577718.560129672</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>571160.875730969</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>926954.049752185</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>1008296.07166832</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1060519.7662693</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1070034.54502798</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.004</t>
+          <t>1003989.42352361</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>984408.568992497</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1099267.05974208</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>1109170.91656561</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>1062688.51392691</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1013567.50857104</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1002328.50694426</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.051</t>
+          <t>1051125.06864695</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>998648.902306324</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>899850.212115466</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>829711.820434529</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2.835</t>
+          <t>2834949.49940005</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.645</t>
+          <t>2645052.93407152</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2.778</t>
+          <t>2778124.56956262</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.273</t>
+          <t>3273322.84204958</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.893</t>
+          <t>2893286.31484983</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>2763548.61738719</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.944</t>
+          <t>2944264.95137069</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2.707</t>
+          <t>2706805.78907168</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.503</t>
+          <t>2503445.04427348</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.298</t>
+          <t>2298071.02932103</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.911</t>
+          <t>1911373.48529223</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>1747270.01857297</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1556553.88842868</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1560008.66602058</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.651</t>
+          <t>1651004.55545206</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7.602</t>
+          <t>7602103.40560799</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6.138</t>
+          <t>6137898.41796814</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.168</t>
+          <t>5168466.01290329</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4.824</t>
+          <t>4823790.51665992</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.984</t>
+          <t>4983506.05930021</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.799</t>
+          <t>4799045.86615095</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4.404</t>
+          <t>4403976.62181365</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3.919</t>
+          <t>3919304.8613324</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3179982.99860866</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.459</t>
+          <t>2459491.15600545</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2.233</t>
+          <t>2232765.52249735</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1945371.60851154</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1594792.61739799</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1350210.74864362</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1570174.43631681</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>732358.591702728</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>662213.127080252</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>653143.590574973</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>677020.411103008</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>651363.723100382</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>750205.700454818</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>694603.571649822</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>642307.742595659</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>589767.231781529</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545487.783741473</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>543036.141184954</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>516730.095986657</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>423672.496682113</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374357.608116693</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>423731.342527341</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6.239</t>
+          <t>6239493.41431475</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5.227</t>
+          <t>5227147.74559972</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4.565</t>
+          <t>4565447.62220502</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4.329</t>
+          <t>4329231.05695781</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4.445</t>
+          <t>4444855.60769461</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.859</t>
+          <t>3858569.41897717</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.413</t>
+          <t>3412512.72197661</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3319988.06680345</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2800498.46167927</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2.348</t>
+          <t>2347849.07476829</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2.124</t>
+          <t>2123805.47255656</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1740102.63786687</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1390345.40021281</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1136624.22676546</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1158128.92006447</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4.361</t>
+          <t>4361115.42272585</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.905</t>
+          <t>3905094.98270357</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.285</t>
+          <t>3285345.00466985</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>3278102.19070015</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.105</t>
+          <t>3105298.19489718</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.804</t>
+          <t>2803677.83775151</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.741</t>
+          <t>2741107.40344836</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.637</t>
+          <t>2636623.11434234</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.769</t>
+          <t>2768625.61091666</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2709855.66230577</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>2435111.07802833</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.207</t>
+          <t>2206886.57774584</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.029</t>
+          <t>2028896.45448774</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2059776.29600876</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.488</t>
+          <t>2488025.6212823</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.807</t>
+          <t>1807018.17560508</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.788</t>
+          <t>1787663.8961694</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.642</t>
+          <t>1642116.60360061</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1635330.69293873</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>1767949.37742072</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>1878001.43775935</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.713</t>
+          <t>1712654.57872439</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1667440.43347577</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>1418910.03134332</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1272655.95759253</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1092964.89236623</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1219163.18944527</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1.004</t>
+          <t>1003761.95102448</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>898688.199856523</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>935015.991092042</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1058405.90971196</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>1086528.30686357</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>1108630.34478</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>1183597.2548443</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1250934.47312512</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.289</t>
+          <t>1289426.68440997</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1279942.96188907</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1081639.60304337</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1018287.69082893</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>928435.820582513</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>898630.31024813</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>835188.595068328</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>744977.988092763</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>640827.110982109</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>649536.947368033</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4.175</t>
+          <t>4175347.49639658</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.855</t>
+          <t>3854890.24549971</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>3835720.39099996</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.607</t>
+          <t>3607065.01113753</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.749</t>
+          <t>3749411.04870227</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.603</t>
+          <t>3603457.40508078</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.056</t>
+          <t>3056433.04497007</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.803</t>
+          <t>2802681.95295092</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>2504066.81493406</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.109</t>
+          <t>2109202.88359233</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.889</t>
+          <t>1888619.33434591</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1714820.21553491</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1458503.68886172</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1150967.24652064</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1343755.64495379</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.996</t>
+          <t>1995564.79150162</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>1881944.22527554</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.902</t>
+          <t>1901531.49494196</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.937</t>
+          <t>1936772.05380898</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>1955662.06974555</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>2183067.79659989</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.173</t>
+          <t>2172651.04322629</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.996</t>
+          <t>1995881.33872735</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.662</t>
+          <t>1661815.16955811</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1476032.61544778</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1388976.72158042</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1271206.90401045</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>1126105.69685799</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>1043373.62388568</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>936855.616814404</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9.767</t>
+          <t>9766958.84881369</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9.326</t>
+          <t>9326030.78741474</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9.067</t>
+          <t>9067445.93448615</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>8.147</t>
+          <t>8147477.34322041</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10.194</t>
+          <t>10194071.4976101</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>9.504</t>
+          <t>9504016.23206263</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8.381</t>
+          <t>8380636.70390718</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>7.212</t>
+          <t>7211744.08157199</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5.678</t>
+          <t>5677776.02116092</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4.209</t>
+          <t>4209083.40629761</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3.439</t>
+          <t>3439280.66921167</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>2917508.78918023</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2.194</t>
+          <t>2194162.01196274</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>1841931.5748117</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>2214673.96612757</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10.285</t>
+          <t>10285347.1339375</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7.987</t>
+          <t>7987486.89128784</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.424</t>
+          <t>7423863.09762337</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9.218</t>
+          <t>9218076.92306591</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14.942</t>
+          <t>14941655.4827737</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>12.045</t>
+          <t>12045435.6804314</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10.178</t>
+          <t>10177986.7952168</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9.077</t>
+          <t>9076883.56725977</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>7.693</t>
+          <t>7693393.35603565</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5.699</t>
+          <t>5699248.10251524</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>4.655</t>
+          <t>4655353.95691632</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>3.624</t>
+          <t>3623790.4650921</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.871</t>
+          <t>2870990.53242077</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>2294393.43523809</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.931</t>
+          <t>2931372.3650427</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4.171</t>
+          <t>4170836.4641802</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.925</t>
+          <t>3924749.0981384</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>3674578.5946504</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3.393</t>
+          <t>3392522.30864386</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.718</t>
+          <t>3717999.60759209</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.568</t>
+          <t>3568176.12537619</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3379794.11972676</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.852</t>
+          <t>2852152.84089639</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2210446.1623732</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.926</t>
+          <t>1925860.27714384</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.821</t>
+          <t>1821174.63285764</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.661</t>
+          <t>1660770.22239329</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1377961.67917801</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.517</t>
+          <t>1516937.59481148</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>1699212.37610068</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2.163</t>
+          <t>2163028.20342785</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>2104001.25202675</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.032</t>
+          <t>2031614.98763066</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2.004</t>
+          <t>2004472.55733757</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.093</t>
+          <t>2093302.30684117</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>2221368.76504173</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.218</t>
+          <t>2217894.87787802</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.026</t>
+          <t>2026179.88840213</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>1803291.32718641</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>1544008.06100477</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>1433382.84613018</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>1348998.9544639</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>1123267.98924926</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1078040.11095328</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1118884.11173154</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>972878.830947649</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>862283.033849521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>886901.872392069</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>918915.462590257</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>935380.766056562</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.996</t>
+          <t>996027.62838063</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1012436.10455655</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>915568.900677333</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>798286.822024351</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>710649.065121436</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>695550.024253672</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>642118.265697792</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>573632.564455885</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>473193.339001596</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>470860.326797766</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.388</t>
+          <t>3387877.14848213</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.275</t>
+          <t>3275368.6976155</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3229549.85754978</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3.138</t>
+          <t>3137769.84914936</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.386</t>
+          <t>3386321.82345122</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.176</t>
+          <t>3176484.17096599</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.986</t>
+          <t>3985697.16067235</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3.591</t>
+          <t>3590900.09879602</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.818</t>
+          <t>2817800.63612483</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2389958.91439925</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2039537.43979249</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.885</t>
+          <t>1885194.87692639</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1557238.93461767</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1385683.31940246</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1511994.19967175</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.587</t>
+          <t>2587429.59922393</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.476</t>
+          <t>2475563.19753159</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.411</t>
+          <t>2410942.83317165</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2630328.22069678</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.475</t>
+          <t>2474758.72045507</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.489</t>
+          <t>2488629.80452836</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>2628416.15345284</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2.687</t>
+          <t>2686701.04845028</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2.618</t>
+          <t>2618017.00711066</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2.522</t>
+          <t>2522390.79644355</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2.301</t>
+          <t>2300628.42481512</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2.198</t>
+          <t>2198118.34496425</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2.053</t>
+          <t>2053138.83642006</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1939549.38513771</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.903</t>
+          <t>1903112.28633618</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1082385.25748597</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1028097.53319523</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>988976.016862717</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>978400.061528258</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>984017.229336613</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>990996.668786415</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>953953.656470635</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>933511.837191333</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>893921.265833423</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870603.660058366</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>847376.348290287</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>814655.623078524</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>741933.769022522</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>702456.105945347</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>675951.251892918</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>8.352</t>
+          <t>8352263.02128603</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.258</t>
+          <t>8258235.27210211</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8.372</t>
+          <t>8371833.86634396</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>8.817</t>
+          <t>8816785.78193947</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8.871</t>
+          <t>8871447.38000383</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9.005</t>
+          <t>9004536.26217333</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9520001.90679393</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>9.562</t>
+          <t>9562183.75425118</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>9.099</t>
+          <t>9099271.4080267</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8.439</t>
+          <t>8438982.49013654</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>7.673</t>
+          <t>7672856.66900778</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>7.013</t>
+          <t>7012930.91975536</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>6.115</t>
+          <t>6114777.60725312</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>5.218</t>
+          <t>5218441.23950145</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>5.726</t>
+          <t>5726246.21156314</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>183.634</t>
+          <t>183633836.643381</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>169.453</t>
+          <t>169453285.664141</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>163.507</t>
+          <t>163507323.418282</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>175.551</t>
+          <t>175550817.213866</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>174.969</t>
+          <t>174969351.203791</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>167.859</t>
+          <t>167859022.785018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>164.303</t>
+          <t>164302801.622222</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>152.6</t>
+          <t>152600197.167144</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>134.137</t>
+          <t>134136588.876644</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>118.719</t>
+          <t>118718598.016658</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>104.984</t>
+          <t>104983995.307666</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>92.312</t>
+          <t>92312193.4217314</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>76.749</t>
+          <t>76749400.2985881</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>68.015</t>
+          <t>68014814.5009251</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>70.852</t>
+          <t>70852468.0693767</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
